--- a/data/trans_dic/POLIPATOLOGIA_5-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,65</t>
+          <t>0,53; 5,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,54</t>
+          <t>0,24; 2,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,35</t>
+          <t>0,95; 3,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,51</t>
+          <t>0,45; 2,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,19</t>
+          <t>0,36; 2,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,33</t>
+          <t>1,26; 4,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,59</t>
+          <t>0,45; 1,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,32</t>
+          <t>0,28; 1,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,11</t>
+          <t>0,2; 1,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>0,91; 2,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,72</t>
+          <t>0,3; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,18</t>
+          <t>0,13; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,21</t>
+          <t>2,01; 5,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,15</t>
+          <t>1,16; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,61</t>
+          <t>2,05; 4,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,66</t>
+          <t>1,41; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,06</t>
+          <t>2,99; 6,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,11</t>
+          <t>0,91; 2,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,73</t>
+          <t>1,2; 2,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,09</t>
+          <t>0,83; 2,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,15</t>
+          <t>2,95; 5,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,88</t>
+          <t>1,1; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,94</t>
+          <t>1,19; 3,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,2</t>
+          <t>1,43; 3,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,37</t>
+          <t>1,88; 7,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,45</t>
+          <t>3,44; 7,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,79</t>
+          <t>4,48; 8,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,11</t>
+          <t>5,19; 9,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,73</t>
+          <t>10,6; 15,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,05</t>
+          <t>2,62; 4,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,72</t>
+          <t>3,16; 5,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,07</t>
+          <t>3,62; 6,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,71</t>
+          <t>5,23; 10,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,86</t>
+          <t>3,84; 8,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,39</t>
+          <t>2,47; 6,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,92</t>
+          <t>3,31; 7,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,79</t>
+          <t>8,87; 13,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,49</t>
+          <t>7,75; 13,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 19,44</t>
+          <t>12,29; 19,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 19,73</t>
+          <t>12,44; 19,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,85; 21,82</t>
+          <t>16,98; 21,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,36</t>
+          <t>6,56; 10,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,28</t>
+          <t>8,16; 12,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,96</t>
+          <t>8,48; 12,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 16,89</t>
+          <t>13,53; 17,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,86; 16,45</t>
+          <t>8,99; 16,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,74</t>
+          <t>10,45; 19,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 11,87</t>
+          <t>5,86; 11,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 18,13</t>
+          <t>12,51; 18,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 21,22</t>
+          <t>13,27; 21,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,36; 24,64</t>
+          <t>16,4; 24,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,26; 28,19</t>
+          <t>19,42; 28,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,47; 79,99</t>
+          <t>27,51; 78,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 17,71</t>
+          <t>12,18; 17,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,59</t>
+          <t>14,72; 20,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,56; 19,11</t>
+          <t>13,82; 19,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,71; 66,91</t>
+          <t>21,66; 67,44</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 22,65</t>
+          <t>12,35; 22,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 25,93</t>
+          <t>15,6; 26,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 22,77</t>
+          <t>14,27; 23,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,55; 38,05</t>
+          <t>29,2; 37,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,06; 27,83</t>
+          <t>18,58; 27,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,67; 40,41</t>
+          <t>30,24; 40,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,31; 33,47</t>
+          <t>23,31; 33,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,18; 51,16</t>
+          <t>44,5; 51,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,94; 24,16</t>
+          <t>17,09; 24,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,13; 33,56</t>
+          <t>26,01; 33,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,1; 28,09</t>
+          <t>20,95; 28,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,56; 44,91</t>
+          <t>39,39; 44,76</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,12</t>
+          <t>2,89; 4,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,49</t>
+          <t>3,12; 4,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,2</t>
+          <t>2,93; 4,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,95</t>
+          <t>6,21; 9,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,71</t>
+          <t>5,91; 7,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,91</t>
+          <t>8,9; 10,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,9</t>
+          <t>8,81; 11,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,76; 35,55</t>
+          <t>15,75; 35,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,69</t>
+          <t>4,57; 5,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,5</t>
+          <t>6,28; 7,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,33</t>
+          <t>6,1; 7,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,61; 23,57</t>
+          <t>11,72; 22,67</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1025</t>
+          <t>0; 977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5192</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>0; 4843</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1629; 17697</t>
+          <t>1671; 18179</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6770</t>
+          <t>0; 6890</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1905; 18144</t>
+          <t>1695; 17832</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5025</t>
+          <t>0; 5045</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4934</t>
+          <t>0; 5134</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8145</t>
+          <t>0; 8463</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5531; 20957</t>
+          <t>5914; 19977</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2689; 15343</t>
+          <t>2731; 16171</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2270; 12340</t>
+          <t>2033; 13299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6097; 22155</t>
+          <t>6455; 22940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6054; 21658</t>
+          <t>6122; 20533</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2964; 17137</t>
+          <t>3624; 17321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1934; 12807</t>
+          <t>2349; 12997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8022; 24473</t>
+          <t>8493; 24621</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1879; 10993</t>
+          <t>1911; 11315</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>889; 8022</t>
+          <t>887; 9137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9025</t>
+          <t>0; 8560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11012; 27968</t>
+          <t>10758; 27653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7728; 21701</t>
+          <t>7971; 22304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14171; 32764</t>
+          <t>14554; 32994</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9348; 24200</t>
+          <t>9313; 24705</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17870; 35900</t>
+          <t>17729; 35563</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11673; 28071</t>
+          <t>12153; 28700</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16165; 38008</t>
+          <t>16646; 36085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11112; 27867</t>
+          <t>11059; 26870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32371; 58117</t>
+          <t>33274; 57334</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5611; 20155</t>
+          <t>5713; 19980</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6421; 24205</t>
+          <t>7327; 22845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9483; 27138</t>
+          <t>9220; 25799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17361; 65388</t>
+          <t>16723; 65115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17960; 38395</t>
+          <t>17737; 36644</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28807; 54142</t>
+          <t>27603; 54283</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32021; 59111</t>
+          <t>33667; 59872</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74944; 112106</t>
+          <t>75572; 112100</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26370; 52229</t>
+          <t>27104; 50998</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40672; 70346</t>
+          <t>38939; 70771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48454; 78678</t>
+          <t>46835; 80083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80934; 171393</t>
+          <t>83764; 171439</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15344; 34247</t>
+          <t>14832; 33790</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10881; 27436</t>
+          <t>10603; 26904</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16152; 37870</t>
+          <t>15829; 38160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50891; 77413</t>
+          <t>49791; 76460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31517; 54510</t>
+          <t>31325; 55621</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55204; 87038</t>
+          <t>55052; 87329</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62321; 98032</t>
+          <t>61828; 94760</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92338; 119540</t>
+          <t>93021; 120434</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52912; 81953</t>
+          <t>51887; 81550</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70209; 107705</t>
+          <t>71616; 108643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85077; 126362</t>
+          <t>82705; 123732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>149498; 187295</t>
+          <t>150108; 190144</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25918; 48123</t>
+          <t>26298; 49015</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31270; 58042</t>
+          <t>32372; 59373</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19675; 39671</t>
+          <t>19577; 39363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46026; 66736</t>
+          <t>46061; 69318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44330; 72786</t>
+          <t>45495; 72653</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57916; 87228</t>
+          <t>58047; 87799</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72754; 106490</t>
+          <t>73360; 108423</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>167097; 486607</t>
+          <t>167352; 476928</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>78010; 112524</t>
+          <t>77387; 112143</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96610; 136648</t>
+          <t>97725; 137394</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96549; 136057</t>
+          <t>98430; 138858</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>212009; 653409</t>
+          <t>211523; 658543</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25367; 47533</t>
+          <t>25926; 46574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38745; 64789</t>
+          <t>38965; 67295</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36488; 58529</t>
+          <t>36680; 61003</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83557; 107576</t>
+          <t>82564; 106840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60313; 92929</t>
+          <t>62052; 93423</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>119306; 157204</t>
+          <t>117609; 156652</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93284; 133955</t>
+          <t>93268; 132664</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>188116; 217834</t>
+          <t>189474; 218177</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92111; 131405</t>
+          <t>92953; 132533</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166937; 214373</t>
+          <t>166172; 213604</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138678; 184592</t>
+          <t>137693; 184578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>280292; 318241</t>
+          <t>279105; 317171</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>92695; 134837</t>
+          <t>94626; 136121</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107465; 153734</t>
+          <t>106968; 156398</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97702; 142580</t>
+          <t>99319; 143874</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>215175; 309745</t>
+          <t>214747; 311928</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>198422; 260679</t>
+          <t>199560; 258014</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>313531; 388151</t>
+          <t>316576; 388206</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>310099; 386289</t>
+          <t>312428; 390815</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>585192; 1319657</t>
+          <t>584704; 1318188</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>306644; 378429</t>
+          <t>303891; 374096</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>436314; 523549</t>
+          <t>438667; 522074</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>420266; 508712</t>
+          <t>422978; 509744</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>832624; 1690428</t>
+          <t>840275; 1625930</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_5-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,5</t>
+          <t>0,28; 2,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,19</t>
+          <t>0,89; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,65</t>
+          <t>0,47; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,36</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,48</t>
+          <t>1,6; 4,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,51</t>
+          <t>0,46; 1,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,34</t>
+          <t>0,26; 1,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,13</t>
+          <t>0,2; 1,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,63</t>
+          <t>1,01; 2,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,77</t>
+          <t>0,29; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,13; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,16</t>
+          <t>1,8; 4,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,23</t>
+          <t>1,13; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,64</t>
+          <t>1,9; 4,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,74</t>
+          <t>1,52; 3,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,01</t>
+          <t>3,43; 6,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,16</t>
+          <t>0,84; 2,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,59</t>
+          <t>1,17; 2,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,02</t>
+          <t>0,86; 2,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,08</t>
+          <t>2,99; 5,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,85</t>
+          <t>1,0; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,72</t>
+          <t>1,07; 3,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,99</t>
+          <t>1,45; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,33</t>
+          <t>4,75; 8,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,11</t>
+          <t>3,23; 7,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,81</t>
+          <t>4,77; 9,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,22</t>
+          <t>4,94; 9,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,72</t>
+          <t>11,07; 14,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,93</t>
+          <t>2,61; 4,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,75</t>
+          <t>3,18; 5,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,18</t>
+          <t>3,72; 6,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,71</t>
+          <t>8,42; 11,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,74</t>
+          <t>4,05; 9,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,27</t>
+          <t>2,48; 6,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,98</t>
+          <t>3,23; 7,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,62</t>
+          <t>8,62; 13,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 13,77</t>
+          <t>7,38; 13,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 19,5</t>
+          <t>12,43; 19,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 19,07</t>
+          <t>12,56; 19,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,98</t>
+          <t>16,63; 21,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,31</t>
+          <t>6,46; 10,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,38</t>
+          <t>8,11; 12,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,69</t>
+          <t>8,59; 12,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 17,14</t>
+          <t>13,3; 16,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,75</t>
+          <t>8,9; 16,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 19,17</t>
+          <t>10,02; 18,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,77</t>
+          <t>5,92; 12,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,51; 18,83</t>
+          <t>11,57; 17,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,27; 21,19</t>
+          <t>13,27; 21,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,4; 24,8</t>
+          <t>15,77; 24,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,42; 28,7</t>
+          <t>19,07; 28,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,51; 78,39</t>
+          <t>26,56; 32,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,65</t>
+          <t>12,21; 17,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,72; 20,7</t>
+          <t>14,49; 20,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,82; 19,5</t>
+          <t>13,75; 19,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 67,44</t>
+          <t>20,15; 24,43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,35; 22,19</t>
+          <t>12,18; 22,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 26,93</t>
+          <t>15,14; 25,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,74</t>
+          <t>14,25; 23,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,2; 37,78</t>
+          <t>28,67; 37,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,58; 27,98</t>
+          <t>18,04; 27,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,24; 40,27</t>
+          <t>30,7; 40,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,31; 33,15</t>
+          <t>22,86; 33,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,5; 51,24</t>
+          <t>44,12; 50,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,09; 24,37</t>
+          <t>17,13; 24,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,01; 33,44</t>
+          <t>25,79; 33,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,95; 28,09</t>
+          <t>21,14; 28,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,39; 44,76</t>
+          <t>38,87; 44,54</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,15</t>
+          <t>2,82; 4,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,56</t>
+          <t>3,13; 4,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,24</t>
+          <t>2,88; 4,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,02</t>
+          <t>7,62; 9,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,64</t>
+          <t>5,89; 7,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,91</t>
+          <t>8,94; 11,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,03</t>
+          <t>8,71; 10,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,75; 35,51</t>
+          <t>15,45; 17,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,62</t>
+          <t>4,56; 5,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,47</t>
+          <t>6,29; 7,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,13; 7,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,67</t>
+          <t>11,87; 13,22</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>8408</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4825</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 977</t>
+          <t>0; 7327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4968</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1671; 18179</t>
+          <t>2047; 18843</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6890</t>
+          <t>0; 6133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5775</t>
+          <t>0; 5708</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1695; 17832</t>
+          <t>2194; 20125</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16698</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5045</t>
+          <t>0; 5053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8463</t>
+          <t>0; 9408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5914; 19977</t>
+          <t>5591; 19885</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2731; 16171</t>
+          <t>2883; 15383</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2033; 13299</t>
+          <t>2680; 13276</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6455; 22940</t>
+          <t>8039; 22417</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6122; 20533</t>
+          <t>6200; 21950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3624; 17321</t>
+          <t>3421; 17287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2349; 12997</t>
+          <t>2277; 12893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8493; 24621</t>
+          <t>9893; 26534</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>48607</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1911; 11315</t>
+          <t>1874; 11399</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>887; 9137</t>
+          <t>912; 9311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8560</t>
+          <t>0; 7932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10758; 27653</t>
+          <t>11197; 29861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7971; 22304</t>
+          <t>7795; 21942</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14554; 32994</t>
+          <t>13541; 32883</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9313; 24705</t>
+          <t>10034; 24354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17729; 35563</t>
+          <t>21376; 39101</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12153; 28700</t>
+          <t>11196; 27859</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16646; 36085</t>
+          <t>16364; 36100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11059; 26870</t>
+          <t>11398; 28158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33274; 57334</t>
+          <t>37219; 62470</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>45728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>95070</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>135905</t>
+          <t>140799</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5713; 19980</t>
+          <t>5169; 19534</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7327; 22845</t>
+          <t>6549; 22595</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9220; 25799</t>
+          <t>9359; 26039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16723; 65115</t>
+          <t>33300; 61452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17737; 36644</t>
+          <t>16677; 36724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27603; 54283</t>
+          <t>29383; 55793</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33667; 59872</t>
+          <t>32068; 59838</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75572; 112100</t>
+          <t>81541; 110443</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27104; 50998</t>
+          <t>26992; 50606</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38939; 70771</t>
+          <t>39161; 70321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46835; 80083</t>
+          <t>48187; 78078</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83764; 171439</t>
+          <t>121053; 160198</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>105258</t>
+          <t>115966</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>182378</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14832; 33790</t>
+          <t>15656; 35637</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10603; 26904</t>
+          <t>10643; 28094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15829; 38160</t>
+          <t>15417; 37321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49791; 76460</t>
+          <t>52507; 84265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31325; 55621</t>
+          <t>29815; 54713</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55052; 87329</t>
+          <t>55644; 87009</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61828; 94760</t>
+          <t>62421; 95866</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93021; 120434</t>
+          <t>101278; 131632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51887; 81550</t>
+          <t>51061; 80405</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71616; 108643</t>
+          <t>71171; 107089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82705; 123732</t>
+          <t>83742; 125437</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>150108; 190144</t>
+          <t>161998; 204178</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>320723</t>
+          <t>129034</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>376617</t>
+          <t>187563</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26298; 49015</t>
+          <t>26052; 47474</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32372; 59373</t>
+          <t>31041; 58270</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19577; 39363</t>
+          <t>19795; 40318</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46061; 69318</t>
+          <t>47110; 69661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45495; 72653</t>
+          <t>45512; 72704</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58047; 87799</t>
+          <t>55840; 87527</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73360; 108423</t>
+          <t>72033; 107625</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>167352; 476928</t>
+          <t>116657; 144436</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>77387; 112143</t>
+          <t>77624; 112879</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>97725; 137394</t>
+          <t>96212; 138905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98430; 138858</t>
+          <t>97935; 137315</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>211523; 658543</t>
+          <t>170478; 206778</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94189</t>
+          <t>102790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>203641</t>
+          <t>221775</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>297830</t>
+          <t>324565</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25926; 46574</t>
+          <t>25567; 46358</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38965; 67295</t>
+          <t>37832; 64618</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36680; 61003</t>
+          <t>36628; 59182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82564; 106840</t>
+          <t>88927; 116558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>62052; 93423</t>
+          <t>60246; 93036</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>117609; 156652</t>
+          <t>119416; 157821</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93268; 132664</t>
+          <t>91487; 132462</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>189474; 218177</t>
+          <t>204968; 236129</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92953; 132533</t>
+          <t>93152; 131969</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166172; 213604</t>
+          <t>164757; 212168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137693; 184578</t>
+          <t>138899; 186072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>279105; 317171</t>
+          <t>301156; 345099</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>296611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>768308</t>
+          <t>612406</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1043545</t>
+          <t>909017</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>94626; 136121</t>
+          <t>92334; 132324</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>106968; 156398</t>
+          <t>107358; 155302</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>99319; 143874</t>
+          <t>97806; 141994</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>214747; 311928</t>
+          <t>269188; 326031</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>199560; 258014</t>
+          <t>198888; 259829</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>316576; 388206</t>
+          <t>318098; 393390</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>312428; 390815</t>
+          <t>308721; 386225</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>584704; 1318188</t>
+          <t>577420; 648180</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>303891; 374096</t>
+          <t>303623; 375812</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>438667; 522074</t>
+          <t>439319; 528206</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>422978; 509744</t>
+          <t>425038; 509279</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>840275; 1625930</t>
+          <t>863262; 960896</t>
         </is>
       </c>
     </row>
